--- a/26-2 Sports Day/예산팀/26-2 Sports Day 예산안.xlsx
+++ b/26-2 Sports Day/예산팀/26-2 Sports Day 예산안.xlsx
@@ -124,18 +124,18 @@
     <t>맘스터치 수원성균관대점</t>
   </si>
   <si>
+    <t>국제처 지원</t>
+  </si>
+  <si>
+    <t>점심(논비건) - 맘스터치 불고기버거 단품 (교환)</t>
+  </si>
+  <si>
     <t>(혼성 계주) 바통</t>
   </si>
   <si>
-    <t>국제처 지원</t>
-  </si>
-  <si>
     <t>브룸</t>
   </si>
   <si>
-    <t>점심(논비건) - 맘스터치 불고기버거 단품 (교환)</t>
-  </si>
-  <si>
     <t>(혼성 계주, 무궁화꽃, 피구, 줄다리기) 트랙 마킹 콘</t>
   </si>
   <si>
@@ -145,45 +145,45 @@
     <t>(혼성 계주) 결승 테이프</t>
   </si>
   <si>
+    <t>써브웨이 수원성균관대점</t>
+  </si>
+  <si>
     <t>(무궁화꽃) 인사이드아웃 복장 세트(간소화 가능)</t>
   </si>
   <si>
+    <t>단체티</t>
+  </si>
+  <si>
     <t>가면으로 대체 가능?</t>
   </si>
   <si>
-    <t>써브웨이 수원성균관대점</t>
+    <t>단체티 - 하이클럽</t>
   </si>
   <si>
     <t xml:space="preserve">(무궁화꽃) 뿅망치 </t>
   </si>
   <si>
-    <t>단체티</t>
-  </si>
-  <si>
     <t>2개 이상</t>
   </si>
   <si>
-    <t>단체티 - 하이클럽</t>
-  </si>
-  <si>
     <t>구매</t>
   </si>
   <si>
     <t>(무궁화꽃, 짝찾기게임) 마이크</t>
   </si>
   <si>
+    <t>단티</t>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>단티</t>
+    <t>https://www.dantee.co.kr/estimate/estimate_register.php?mode=update&amp;estimateNo=2608170901037278&amp;pwtoken=668a2ae597a601d877a24840626bb6e7</t>
   </si>
   <si>
     <t>(무궁화꽃) 스피커</t>
   </si>
   <si>
-    <t>https://www.dantee.co.kr/estimate/estimate_register.php?mode=update&amp;estimateNo=2608170901037278&amp;pwtoken=668a2ae597a601d877a24840626bb6e7</t>
-  </si>
-  <si>
     <t xml:space="preserve">(제기차기) 제기 </t>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>(판뒤집기) 양면 색깔 판</t>
   </si>
   <si>
+    <t>단체티 - 교환학생</t>
+  </si>
+  <si>
     <t xml:space="preserve">(병뚜껑컬링) 과녁판 </t>
   </si>
   <si>
@@ -211,18 +214,27 @@
     <t xml:space="preserve">(병뚜껑컬링) 병뚜껑 </t>
   </si>
   <si>
+    <t>음료</t>
+  </si>
+  <si>
+    <t>(물) 탐사수 무라벨 500ml*200개 (총 400개)</t>
+  </si>
+  <si>
     <t>물 활용</t>
   </si>
   <si>
     <t>(페트병세우기) 물이 일부 들어있는 페트병</t>
   </si>
   <si>
+    <t>쿠팡</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/5625704601?itemId=19013170090&amp;vendorItemId=86137790576&amp;q=%EB%AC%BC+500ml&amp;searchId=0382ea52557456&amp;sourceType=search&amp;itemsCount=60&amp;searchRank=3&amp;rank=3&amp;traceId=mt2eofot</t>
+  </si>
+  <si>
     <t xml:space="preserve">(피구) 피구공 </t>
   </si>
   <si>
-    <t>단체티 - 교환학생</t>
-  </si>
-  <si>
     <t>(피구, 줄다리기) 팀별 조끼</t>
   </si>
   <si>
@@ -232,33 +244,27 @@
     <t>(피구) 슬픔이 감정 캐릭터 머리띠</t>
   </si>
   <si>
-    <t>음료</t>
-  </si>
-  <si>
-    <t>(물) 탐사수 무라벨 500ml*200개 (총 400개)</t>
-  </si>
-  <si>
     <t>머리띠 없음 가면으로 대체 가능?</t>
   </si>
   <si>
     <t>(피구, 줄다리기) 점수판</t>
   </si>
   <si>
-    <t>쿠팡</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/5625704601?itemId=19013170090&amp;vendorItemId=86137790576&amp;q=%EB%AC%BC+500ml&amp;searchId=0382ea52557456&amp;sourceType=search&amp;itemsCount=60&amp;searchRank=3&amp;rank=3&amp;traceId=mt2eofot</t>
-  </si>
-  <si>
     <t>화이트보드 대체?</t>
   </si>
   <si>
+    <t>(음료) 게토레이 레몬 300ml*120개 (총 216개)</t>
+  </si>
+  <si>
     <t>(피구, 감정몸짓퀴즈) 타이머</t>
   </si>
   <si>
     <t>사야됨?</t>
   </si>
   <si>
+    <t>https://www.coupang.com/vp/products/1650278?itemId=28712633479&amp;vendorItemId=95653362582&amp;q=%EA%B2%8C%ED%86%A0%EB%A0%9D&amp;searchId=2395745a1367533&amp;sourceType=search&amp;itemsCount=60&amp;searchRank=8&amp;rank=8&amp;traceId=mt2f5sxp</t>
+  </si>
+  <si>
     <t>(줄다리기) 줄다리기용 로프</t>
   </si>
   <si>
@@ -274,12 +280,12 @@
     <t>(줄다리기) 미끄럼 방지 장갑(안전용)</t>
   </si>
   <si>
+    <t>(음료) 게토레이 레몬 300ml*48개</t>
+  </si>
+  <si>
     <t>(비어퐁) 비어퐁용 컵</t>
   </si>
   <si>
-    <t>(음료) 게토레이 레몬 300ml*120개 (총 216개)</t>
-  </si>
-  <si>
     <t>10개 이상</t>
   </si>
   <si>
@@ -289,12 +295,12 @@
     <t>(비어퐁) 탁구공</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/1650278?itemId=28712633479&amp;vendorItemId=95653362582&amp;q=%EA%B2%8C%ED%86%A0%EB%A0%9D&amp;searchId=2395745a1367533&amp;sourceType=search&amp;itemsCount=60&amp;searchRank=8&amp;rank=8&amp;traceId=mt2f5sxp</t>
-  </si>
-  <si>
     <t>5개 이상</t>
   </si>
   <si>
+    <t>https://www.coupang.com/vp/products/1650278?itemId=28712633427&amp;vendorItemId=95653362488&amp;q=%EA%B2%8C%ED%86%A0%EB%A0%9D&amp;searchId=2395745a1367533&amp;sourceType=search&amp;itemsCount=60&amp;searchRank=2&amp;rank=2&amp;traceId=mt2f100r</t>
+  </si>
+  <si>
     <t>(비어퐁) 테이블</t>
   </si>
   <si>
@@ -304,10 +310,16 @@
     <t>(비어퐁, 감정몸짓퀴즈) 도장</t>
   </si>
   <si>
+    <t>간식</t>
+  </si>
+  <si>
+    <t>(간식/비건) 소이조이 바나나 비건 단백질바 (총 12개)</t>
+  </si>
+  <si>
     <t>(비어퐁, 감정몸짓퀴즈) 스탬프 용지</t>
   </si>
   <si>
-    <t>(음료) 게토레이 레몬 300ml*48개</t>
+    <t>https://www.coupang.com/vp/products/8532976813?itemId=24699868616&amp;vendorItemId=91805941787&amp;q=%EC%86%8C%EC%9D%B4%EC%A1%B0%EC%9D%B4+%EB%B0%94%EB%82%98%EB%82%98&amp;searchId=8750072010036413&amp;sourceType=search&amp;itemsCount=60&amp;searchRank=0&amp;rank=0&amp;traceId=mt84v2zo</t>
   </si>
   <si>
     <t>(감정몸짓퀴즈) 감정 카드 - 기쁨/슬픔/분노/까칠/소심/불안/당황 등</t>
@@ -316,24 +328,12 @@
     <t>20장 이상</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/1650278?itemId=28712633427&amp;vendorItemId=95653362488&amp;q=%EA%B2%8C%ED%86%A0%EB%A0%9D&amp;searchId=2395745a1367533&amp;sourceType=search&amp;itemsCount=60&amp;searchRank=2&amp;rank=2&amp;traceId=mt2f100r</t>
-  </si>
-  <si>
     <t>우승 트로피</t>
   </si>
   <si>
     <t>우승 메달</t>
   </si>
   <si>
-    <t>간식</t>
-  </si>
-  <si>
-    <t>(간식/비건) 소이조이 바나나 비건 단백질바 (총 12개)</t>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8532976813?itemId=24699868616&amp;vendorItemId=91805941787&amp;q=%EC%86%8C%EC%9D%B4%EC%A1%B0%EC%9D%B4+%EB%B0%94%EB%82%98%EB%82%98&amp;searchId=8750072010036413&amp;sourceType=search&amp;itemsCount=60&amp;searchRank=0&amp;rank=0&amp;traceId=mt84v2zo</t>
-  </si>
-  <si>
     <t>(간식/논비건) 닥터유 에너지바 468g*17개*3set (총 204개)</t>
   </si>
   <si>
@@ -454,13 +454,13 @@
     <t>총 지출 금액</t>
   </si>
   <si>
-    <t>행사 수입(예상) 15,000원*150명</t>
+    <t>행사 수입(예상) 15,000원*170명</t>
   </si>
   <si>
     <t>국제처 지원 금액</t>
   </si>
   <si>
-    <t>하이클럽 점심 (53*5,200=275,600원), 단체티((53+150))*9,460=2,195,980원)</t>
+    <t>하이클럽 점심 (47*5,200=244,400원), 단체티((47+170))*10,000=2,170,000원)</t>
   </si>
   <si>
     <t>계</t>
@@ -725,55 +725,55 @@
     <xf borderId="8" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
+    <xf borderId="12" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="11" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="11" fillId="3" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="3" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf borderId="13" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -807,23 +807,23 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="13" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="13" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="14" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
@@ -1131,7 +1131,7 @@
         <v>6</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" s="11"/>
     </row>
@@ -1170,53 +1170,53 @@
       <c r="F6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="16" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="18">
-        <v>53.0</v>
-      </c>
-      <c r="D7" s="20">
+      <c r="C7" s="20">
+        <v>47.0</v>
+      </c>
+      <c r="D7" s="22">
         <v>5200.0</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="24">
         <f t="shared" ref="E7:E12" si="1">D7*C7</f>
-        <v>275600</v>
-      </c>
-      <c r="F7" s="29" t="s">
+        <v>244400</v>
+      </c>
+      <c r="F7" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="29" t="s">
         <v>27</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="J7" s="32" t="s">
+      <c r="J7" s="31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32"/>
+      <c r="B8" s="23" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="33"/>
-      <c r="B8" s="23" t="s">
-        <v>31</v>
-      </c>
       <c r="C8" s="23">
-        <v>140.0</v>
+        <v>160.0</v>
       </c>
       <c r="D8" s="34">
         <v>5200.0</v>
       </c>
       <c r="E8" s="35">
         <f t="shared" si="1"/>
-        <v>728000</v>
+        <v>832000</v>
       </c>
       <c r="F8" s="36" t="s">
         <v>23</v>
@@ -1224,10 +1224,10 @@
       <c r="G8" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9">
-      <c r="A9" s="33"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="23" t="s">
         <v>24</v>
       </c>
@@ -1245,64 +1245,64 @@
         <v>25</v>
       </c>
       <c r="G9" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="26"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="25"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="s">
+      <c r="B10" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="39" t="s">
-        <v>41</v>
-      </c>
       <c r="C10" s="39">
-        <v>53.0</v>
+        <v>47.0</v>
       </c>
       <c r="D10" s="40">
-        <v>9460.0</v>
+        <v>15200.0</v>
       </c>
       <c r="E10" s="41">
         <f t="shared" si="1"/>
-        <v>501380</v>
+        <v>714400</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="44"/>
       <c r="B11" s="39" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C11" s="39">
-        <v>150.0</v>
+        <v>170.0</v>
       </c>
       <c r="D11" s="40">
-        <v>9460.0</v>
+        <v>15200.0</v>
       </c>
       <c r="E11" s="41">
         <f t="shared" si="1"/>
-        <v>1419000</v>
+        <v>2584000</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="46" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>46</v>
       </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="44" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C12" s="23">
         <v>2.0</v>
@@ -1315,17 +1315,17 @@
         <v>74980</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="H12" s="25"/>
+        <v>63</v>
+      </c>
+      <c r="H12" s="26"/>
     </row>
     <row r="13">
       <c r="A13" s="44"/>
       <c r="B13" s="23" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C13" s="23">
         <v>1.0</v>
@@ -1337,17 +1337,17 @@
         <v>75700.0</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G13" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" s="25"/>
+        <v>74</v>
+      </c>
+      <c r="H13" s="26"/>
     </row>
     <row r="14">
       <c r="A14" s="44"/>
       <c r="B14" s="23" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C14" s="23">
         <v>2.0</v>
@@ -1360,19 +1360,19 @@
         <v>60560</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="25"/>
+        <v>86</v>
+      </c>
+      <c r="H14" s="26"/>
     </row>
     <row r="15">
       <c r="A15" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C15" s="23">
         <v>1.0</v>
@@ -1385,12 +1385,12 @@
         <v>17100</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="H15" s="25"/>
+        <v>62</v>
+      </c>
+      <c r="G15" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" s="26"/>
     </row>
     <row r="16">
       <c r="A16" s="44"/>
@@ -1408,12 +1408,12 @@
         <v>143040</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="H16" s="25"/>
+      <c r="H16" s="26"/>
     </row>
     <row r="17">
       <c r="A17" s="44"/>
@@ -1431,12 +1431,12 @@
         <v>85050</v>
       </c>
       <c r="F17" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="H17" s="25"/>
+      <c r="H17" s="26"/>
     </row>
     <row r="18">
       <c r="A18" s="44" t="s">
@@ -1456,12 +1456,12 @@
         <v>26200</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G18" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="H18" s="25"/>
+      <c r="H18" s="26"/>
     </row>
     <row r="19">
       <c r="A19" s="44"/>
@@ -1479,12 +1479,12 @@
         <v>27000</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="H19" s="25"/>
+      <c r="H19" s="26"/>
     </row>
     <row r="20">
       <c r="A20" s="44"/>
@@ -1502,12 +1502,12 @@
         <v>5900</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G20" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="H20" s="25"/>
+      <c r="H20" s="26"/>
     </row>
     <row r="21">
       <c r="A21" s="44"/>
@@ -1525,12 +1525,12 @@
         <v>9820</v>
       </c>
       <c r="F21" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="H21" s="25"/>
+      <c r="H21" s="26"/>
     </row>
     <row r="22">
       <c r="A22" s="44"/>
@@ -1548,12 +1548,12 @@
         <v>11900</v>
       </c>
       <c r="F22" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="H22" s="25"/>
+      <c r="H22" s="26"/>
     </row>
     <row r="23">
       <c r="A23" s="44" t="s">
@@ -1573,12 +1573,12 @@
         <v>21000</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="H23" s="25"/>
+      <c r="H23" s="26"/>
     </row>
     <row r="24">
       <c r="A24" s="44"/>
@@ -1596,12 +1596,12 @@
         <v>98800</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="H24" s="25"/>
+      <c r="H24" s="26"/>
     </row>
     <row r="25">
       <c r="A25" s="55"/>
@@ -1619,12 +1619,12 @@
         <v>3100</v>
       </c>
       <c r="F25" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="H25" s="25"/>
+      <c r="H25" s="26"/>
     </row>
     <row r="26">
       <c r="A26" s="56"/>
@@ -1642,12 +1642,12 @@
         <v>9900</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26" s="49" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="25"/>
+      <c r="H26" s="26"/>
     </row>
     <row r="27">
       <c r="A27" s="56"/>
@@ -1665,12 +1665,12 @@
         <v>14200</v>
       </c>
       <c r="F27" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G27" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="H27" s="25"/>
+      <c r="H27" s="26"/>
     </row>
     <row r="28">
       <c r="A28" s="56"/>
@@ -1688,22 +1688,22 @@
         <v>10430</v>
       </c>
       <c r="F28" s="57"/>
-      <c r="G28" s="51" t="s">
+      <c r="G28" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="H28" s="25"/>
+      <c r="H28" s="26"/>
     </row>
     <row r="29">
       <c r="A29" s="56"/>
       <c r="B29" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="C29" s="27"/>
+      <c r="C29" s="30"/>
       <c r="D29" s="58"/>
       <c r="E29" s="35"/>
       <c r="F29" s="36"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
     </row>
     <row r="30">
       <c r="A30" s="56"/>
@@ -1723,10 +1723,10 @@
       <c r="F30" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G30" s="51" t="s">
+      <c r="G30" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="H30" s="25"/>
+      <c r="H30" s="26"/>
     </row>
     <row r="31">
       <c r="A31" s="55" t="s">
@@ -1748,10 +1748,10 @@
       <c r="F31" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G31" s="51" t="s">
+      <c r="G31" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="H31" s="25"/>
+      <c r="H31" s="26"/>
     </row>
     <row r="32">
       <c r="A32" s="56"/>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F32" s="61"/>
       <c r="G32" s="62"/>
-      <c r="H32" s="25"/>
+      <c r="H32" s="26"/>
     </row>
     <row r="33">
       <c r="A33" s="56"/>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="F33" s="59"/>
       <c r="G33" s="62"/>
-      <c r="H33" s="25"/>
+      <c r="H33" s="26"/>
     </row>
     <row r="34">
       <c r="A34" s="56"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="62"/>
-      <c r="H34" s="25"/>
+      <c r="H34" s="26"/>
     </row>
     <row r="35">
       <c r="A35" s="56"/>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="F35" s="59"/>
       <c r="G35" s="62"/>
-      <c r="H35" s="25"/>
+      <c r="H35" s="26"/>
     </row>
     <row r="36">
       <c r="A36" s="55"/>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="F36" s="59"/>
       <c r="G36" s="62"/>
-      <c r="H36" s="25"/>
+      <c r="H36" s="26"/>
     </row>
     <row r="37">
       <c r="A37" s="56"/>
@@ -1841,78 +1841,78 @@
       </c>
       <c r="F37" s="59"/>
       <c r="G37" s="62"/>
-      <c r="H37" s="25"/>
+      <c r="H37" s="26"/>
     </row>
     <row r="38">
       <c r="A38" s="56"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="25"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="26"/>
     </row>
     <row r="39">
       <c r="A39" s="56"/>
       <c r="B39" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C39" s="27"/>
+      <c r="C39" s="30"/>
       <c r="D39" s="64"/>
       <c r="E39" s="64">
         <f>-SUM(E7:E37)</f>
-        <v>-3723660</v>
-      </c>
-      <c r="F39" s="27"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="25"/>
+        <v>-5174480</v>
+      </c>
+      <c r="F39" s="30"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="26"/>
     </row>
     <row r="40">
       <c r="A40" s="56"/>
       <c r="B40" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="C40" s="27"/>
+      <c r="C40" s="30"/>
       <c r="D40" s="64"/>
       <c r="E40" s="35">
-        <f>15000*150</f>
-        <v>2250000</v>
-      </c>
-      <c r="F40" s="27"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="25"/>
+        <f>15000*170</f>
+        <v>2550000</v>
+      </c>
+      <c r="F40" s="30"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="26"/>
     </row>
     <row r="41">
       <c r="A41" s="56"/>
       <c r="B41" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="C41" s="27"/>
+      <c r="C41" s="30"/>
       <c r="D41" s="64"/>
       <c r="E41" s="35">
-        <f>53*5200+203*9460</f>
-        <v>2195980</v>
-      </c>
-      <c r="F41" s="27"/>
+        <f>47*5200+217*10000</f>
+        <v>2414400</v>
+      </c>
+      <c r="F41" s="30"/>
       <c r="G41" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="H41" s="25"/>
+      <c r="H41" s="26"/>
     </row>
     <row r="42">
       <c r="A42" s="56"/>
       <c r="B42" s="65" t="s">
         <v>141</v>
       </c>
-      <c r="C42" s="49"/>
-      <c r="D42" s="49"/>
+      <c r="C42" s="50"/>
+      <c r="D42" s="50"/>
       <c r="E42" s="66">
         <f>E39+E40+E41</f>
-        <v>722320</v>
-      </c>
-      <c r="F42" s="49"/>
-      <c r="G42" s="50"/>
+        <v>-210080</v>
+      </c>
+      <c r="F42" s="50"/>
+      <c r="G42" s="51"/>
       <c r="H42" s="7"/>
     </row>
     <row r="43">
@@ -1961,7 +1961,7 @@
         <v>20099.0</v>
       </c>
       <c r="F49" s="70">
-        <v>9460.0</v>
+        <v>9500.0</v>
       </c>
       <c r="G49" s="48"/>
     </row>
@@ -1971,65 +1971,65 @@
         <v>143</v>
       </c>
       <c r="C50" s="71">
-        <f t="shared" ref="C50:F50" si="4">53*5200+203*10000</f>
-        <v>2305600</v>
+        <f t="shared" ref="C50:F50" si="4">47*5200+217*10000</f>
+        <v>2414400</v>
       </c>
       <c r="D50" s="71">
         <f t="shared" si="4"/>
-        <v>2305600</v>
+        <v>2414400</v>
       </c>
       <c r="E50" s="71">
         <f t="shared" si="4"/>
-        <v>2305600</v>
+        <v>2414400</v>
       </c>
       <c r="F50" s="71">
         <f t="shared" si="4"/>
-        <v>2305600</v>
+        <v>2414400</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="33"/>
+      <c r="A51" s="32"/>
       <c r="B51" s="71" t="s">
         <v>144</v>
       </c>
       <c r="C51" s="72">
-        <f t="shared" ref="C51:F51" si="5">15000*150</f>
-        <v>2250000</v>
+        <f t="shared" ref="C51:F51" si="5">15000*170</f>
+        <v>2550000</v>
       </c>
       <c r="D51" s="72">
         <f t="shared" si="5"/>
-        <v>2250000</v>
+        <v>2550000</v>
       </c>
       <c r="E51" s="72">
         <f t="shared" si="5"/>
-        <v>2250000</v>
+        <v>2550000</v>
       </c>
       <c r="F51" s="72">
         <f t="shared" si="5"/>
-        <v>2250000</v>
+        <v>2550000</v>
       </c>
       <c r="G51" s="48"/>
     </row>
     <row r="52">
-      <c r="A52" s="33"/>
+      <c r="A52" s="32"/>
       <c r="B52" s="71" t="s">
         <v>145</v>
       </c>
       <c r="C52" s="72">
         <f t="shared" ref="C52:F52" si="6">C50+C51</f>
-        <v>4555600</v>
+        <v>4964400</v>
       </c>
       <c r="D52" s="72">
         <f t="shared" si="6"/>
-        <v>4555600</v>
+        <v>4964400</v>
       </c>
       <c r="E52" s="72">
         <f t="shared" si="6"/>
-        <v>4555600</v>
+        <v>4964400</v>
       </c>
       <c r="F52" s="72">
         <f t="shared" si="6"/>
-        <v>4555600</v>
+        <v>4964400</v>
       </c>
       <c r="G52" s="48"/>
     </row>
@@ -2038,20 +2038,20 @@
         <v>146</v>
       </c>
       <c r="C53" s="68">
-        <f t="shared" ref="C53:F53" si="7">sum($E$7:$E$9,$E$12:$E$38)+203*C49</f>
-        <v>4798748</v>
+        <f t="shared" ref="C53:F53" si="7">sum($E$7:$E$9,$E$12:$E$38)+217*C49</f>
+        <v>5078132</v>
       </c>
       <c r="D53" s="68">
         <f t="shared" si="7"/>
-        <v>4888880</v>
+        <v>5174480</v>
       </c>
       <c r="E53" s="68">
         <f t="shared" si="7"/>
-        <v>5883377</v>
+        <v>6237563</v>
       </c>
       <c r="F53" s="68">
         <f t="shared" si="7"/>
-        <v>3723660</v>
+        <v>3937580</v>
       </c>
     </row>
     <row r="54">
@@ -2060,19 +2060,19 @@
       </c>
       <c r="C54" s="67">
         <f>C52-C53</f>
-        <v>-243148</v>
+        <v>-113732</v>
       </c>
       <c r="D54" s="67">
         <f>C52-D53</f>
-        <v>-333280</v>
+        <v>-210080</v>
       </c>
       <c r="E54" s="67">
         <f t="shared" ref="E54:F54" si="8">E52-E53</f>
-        <v>-1327777</v>
+        <v>-1273163</v>
       </c>
       <c r="F54" s="67">
         <f t="shared" si="8"/>
-        <v>831940</v>
+        <v>1026820</v>
       </c>
       <c r="G54" s="48"/>
     </row>
@@ -2088,19 +2088,19 @@
       </c>
       <c r="C56" s="67">
         <f t="shared" ref="C56:F56" si="9">C51-C53</f>
-        <v>-2548748</v>
+        <v>-2528132</v>
       </c>
       <c r="D56" s="67">
         <f t="shared" si="9"/>
-        <v>-2638880</v>
+        <v>-2624480</v>
       </c>
       <c r="E56" s="67">
         <f t="shared" si="9"/>
-        <v>-3633377</v>
+        <v>-3687563</v>
       </c>
       <c r="F56" s="67">
         <f t="shared" si="9"/>
-        <v>-1473660</v>
+        <v>-1387580</v>
       </c>
     </row>
     <row r="57">
@@ -2272,7 +2272,7 @@
         <v>6</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4" s="11"/>
     </row>
@@ -2317,22 +2317,22 @@
       <c r="H6" s="11"/>
     </row>
     <row r="7">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="15">
         <v>180.0</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="17">
         <v>5200.0</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="19">
         <v>936000.0</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="22"/>
+      <c r="G7" s="21"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8">
@@ -2342,43 +2342,43 @@
       <c r="C8" s="23">
         <v>23.0</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="19">
         <v>5200.0</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="19">
         <v>119600.0</v>
       </c>
       <c r="F8" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="25"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10">
-      <c r="A10" s="30"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="23" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="23">
         <v>7.0</v>
       </c>
-      <c r="D10" s="27"/>
+      <c r="D10" s="30"/>
       <c r="E10" s="23"/>
       <c r="F10" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="24"/>
-      <c r="H10" s="25"/>
+        <v>31</v>
+      </c>
+      <c r="G10" s="25"/>
+      <c r="H10" s="26"/>
     </row>
     <row r="11">
       <c r="B11" s="23" t="s">
@@ -2387,13 +2387,13 @@
       <c r="C11" s="23">
         <v>30.0</v>
       </c>
-      <c r="D11" s="27"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="23"/>
       <c r="F11" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="24"/>
-      <c r="H11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="26"/>
     </row>
     <row r="12">
       <c r="B12" s="23" t="s">
@@ -2402,36 +2402,36 @@
       <c r="C12" s="23">
         <v>1.0</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
       <c r="F12" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G12" s="37"/>
-      <c r="H12" s="25"/>
+      <c r="H12" s="26"/>
     </row>
     <row r="13">
       <c r="A13" s="38"/>
       <c r="B13" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="23">
         <v>1.0</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="23"/>
       <c r="G13" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="25"/>
+        <v>38</v>
+      </c>
+      <c r="H13" s="26"/>
     </row>
     <row r="14">
       <c r="B14" s="23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" s="23"/>
       <c r="E14" s="23"/>
@@ -2439,52 +2439,52 @@
         <v>42</v>
       </c>
       <c r="G14" s="37"/>
-      <c r="H14" s="25"/>
+      <c r="H14" s="26"/>
     </row>
     <row r="15">
       <c r="B15" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
+        <v>45</v>
+      </c>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
       <c r="F15" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G15" s="37"/>
-      <c r="H15" s="25"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16">
       <c r="B16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
+        <v>47</v>
+      </c>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
       <c r="F16" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G16" s="37"/>
-      <c r="H16" s="25"/>
+      <c r="H16" s="26"/>
     </row>
     <row r="17">
       <c r="B17" s="23" t="s">
         <v>48</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="27"/>
+      <c r="E17" s="30"/>
       <c r="F17" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" s="24"/>
-      <c r="H17" s="25"/>
+        <v>31</v>
+      </c>
+      <c r="G17" s="25"/>
+      <c r="H17" s="26"/>
     </row>
     <row r="18">
       <c r="A18" s="38"/>
@@ -2494,27 +2494,27 @@
       <c r="C18" s="23">
         <v>1.0</v>
       </c>
-      <c r="D18" s="27"/>
+      <c r="D18" s="30"/>
       <c r="E18" s="23"/>
       <c r="F18" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="24"/>
-      <c r="H18" s="25"/>
+        <v>31</v>
+      </c>
+      <c r="G18" s="25"/>
+      <c r="H18" s="26"/>
     </row>
     <row r="19">
       <c r="A19" s="38"/>
       <c r="B19" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
       <c r="F19" s="23"/>
       <c r="G19" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="H19" s="25"/>
+      <c r="H19" s="26"/>
     </row>
     <row r="20">
       <c r="A20" s="38"/>
@@ -2527,384 +2527,384 @@
       <c r="D20" s="23"/>
       <c r="E20" s="23"/>
       <c r="F20" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="G20" s="24"/>
-      <c r="H20" s="25"/>
+        <v>31</v>
+      </c>
+      <c r="G20" s="25"/>
+      <c r="H20" s="26"/>
     </row>
     <row r="21">
       <c r="B21" s="23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="23">
         <v>1.0</v>
       </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="23"/>
       <c r="G21" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H21" s="25"/>
+        <v>56</v>
+      </c>
+      <c r="H21" s="26"/>
     </row>
     <row r="22">
       <c r="A22" s="38"/>
       <c r="B22" s="23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" s="23">
         <v>3.0</v>
       </c>
-      <c r="D22" s="27"/>
+      <c r="D22" s="30"/>
       <c r="E22" s="23"/>
       <c r="F22" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22" s="24"/>
-      <c r="H22" s="25"/>
+        <v>60</v>
+      </c>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26"/>
     </row>
     <row r="23">
       <c r="B23" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
+        <v>61</v>
+      </c>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
       <c r="E23" s="23"/>
       <c r="F23" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23" s="24"/>
-      <c r="H23" s="25"/>
+        <v>60</v>
+      </c>
+      <c r="G23" s="25"/>
+      <c r="H23" s="26"/>
     </row>
     <row r="24">
       <c r="A24" s="38"/>
       <c r="B24" s="23" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C24" s="23">
         <v>2.0</v>
       </c>
-      <c r="D24" s="27"/>
+      <c r="D24" s="30"/>
       <c r="E24" s="23"/>
       <c r="F24" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="24"/>
-      <c r="H24" s="25"/>
+        <v>31</v>
+      </c>
+      <c r="G24" s="25"/>
+      <c r="H24" s="26"/>
     </row>
     <row r="25">
-      <c r="A25" s="45"/>
+      <c r="A25" s="46"/>
       <c r="B25" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
+        <v>65</v>
+      </c>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
       <c r="G25" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="H25" s="25"/>
+        <v>66</v>
+      </c>
+      <c r="H25" s="26"/>
     </row>
     <row r="26">
-      <c r="A26" s="45"/>
+      <c r="A26" s="46"/>
       <c r="B26" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
+        <v>67</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
       <c r="G26" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="H26" s="25"/>
+        <v>68</v>
+      </c>
+      <c r="H26" s="26"/>
     </row>
     <row r="27">
-      <c r="A27" s="45"/>
+      <c r="A27" s="46"/>
       <c r="B27" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
+        <v>69</v>
+      </c>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
       <c r="G27" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="H27" s="25"/>
+      <c r="H27" s="26"/>
     </row>
     <row r="28">
-      <c r="A28" s="45"/>
+      <c r="A28" s="46"/>
       <c r="B28" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="23">
         <v>2.0</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
       <c r="G28" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28" s="25"/>
+        <v>73</v>
+      </c>
+      <c r="H28" s="26"/>
     </row>
     <row r="29">
-      <c r="A29" s="45"/>
+      <c r="A29" s="46"/>
       <c r="B29" s="23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" s="27"/>
+        <v>76</v>
+      </c>
+      <c r="D29" s="30"/>
       <c r="E29" s="23"/>
       <c r="F29" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G29" s="24"/>
-      <c r="H29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
     </row>
     <row r="30">
-      <c r="A30" s="45"/>
+      <c r="A30" s="46"/>
       <c r="B30" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
+        <v>77</v>
+      </c>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
       <c r="G30" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H30" s="25"/>
+        <v>56</v>
+      </c>
+      <c r="H30" s="26"/>
     </row>
     <row r="31">
-      <c r="A31" s="45"/>
+      <c r="A31" s="46"/>
       <c r="B31" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
+        <v>78</v>
+      </c>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
       <c r="G31" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="H31" s="25"/>
+        <v>73</v>
+      </c>
+      <c r="H31" s="26"/>
     </row>
     <row r="32">
-      <c r="A32" s="45"/>
+      <c r="A32" s="46"/>
       <c r="B32" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
+        <v>79</v>
+      </c>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
       <c r="E32" s="23"/>
       <c r="F32" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" s="24"/>
-      <c r="H32" s="25"/>
+        <v>31</v>
+      </c>
+      <c r="G32" s="25"/>
+      <c r="H32" s="26"/>
     </row>
     <row r="33">
-      <c r="A33" s="45"/>
+      <c r="A33" s="46"/>
       <c r="B33" s="23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="27"/>
+        <v>82</v>
+      </c>
+      <c r="D33" s="30"/>
       <c r="E33" s="23"/>
       <c r="F33" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="G33" s="24"/>
-      <c r="H33" s="25"/>
+        <v>83</v>
+      </c>
+      <c r="G33" s="25"/>
+      <c r="H33" s="26"/>
     </row>
     <row r="34">
-      <c r="A34" s="45"/>
+      <c r="A34" s="46"/>
       <c r="B34" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" s="27"/>
+        <v>85</v>
+      </c>
+      <c r="D34" s="30"/>
       <c r="E34" s="23"/>
       <c r="F34" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="G34" s="24"/>
-      <c r="H34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
     </row>
     <row r="35">
-      <c r="A35" s="45"/>
+      <c r="A35" s="46"/>
       <c r="B35" s="23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C35" s="23">
         <v>2.0</v>
       </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
       <c r="F35" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G35" s="37"/>
-      <c r="H35" s="25"/>
+      <c r="H35" s="26"/>
     </row>
     <row r="36">
-      <c r="A36" s="45"/>
+      <c r="A36" s="46"/>
       <c r="B36" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" s="27"/>
+        <v>88</v>
+      </c>
+      <c r="C36" s="30"/>
       <c r="D36" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
       <c r="G36" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H36" s="25"/>
+        <v>56</v>
+      </c>
+      <c r="H36" s="26"/>
     </row>
     <row r="37">
-      <c r="A37" s="45"/>
+      <c r="A37" s="46"/>
       <c r="B37" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="27"/>
+        <v>89</v>
+      </c>
+      <c r="C37" s="30"/>
       <c r="D37" s="23"/>
-      <c r="E37" s="27"/>
+      <c r="E37" s="30"/>
       <c r="F37" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="G37" s="24"/>
-      <c r="H37" s="25"/>
+        <v>31</v>
+      </c>
+      <c r="G37" s="25"/>
+      <c r="H37" s="26"/>
     </row>
     <row r="38">
-      <c r="A38" s="45"/>
+      <c r="A38" s="46"/>
       <c r="B38" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="27"/>
+        <v>92</v>
+      </c>
+      <c r="C38" s="30"/>
       <c r="D38" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
       <c r="G38" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H38" s="25"/>
+        <v>56</v>
+      </c>
+      <c r="H38" s="26"/>
     </row>
     <row r="39">
-      <c r="A39" s="45"/>
+      <c r="A39" s="46"/>
       <c r="B39" s="23" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D39" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
       <c r="G39" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H39" s="25"/>
+        <v>56</v>
+      </c>
+      <c r="H39" s="26"/>
     </row>
     <row r="40">
-      <c r="A40" s="45"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="25"/>
+      <c r="A40" s="46"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="26"/>
     </row>
     <row r="41">
-      <c r="A41" s="45"/>
+      <c r="A41" s="46"/>
       <c r="B41" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
+        <v>96</v>
+      </c>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
       <c r="F41" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="G41" s="24"/>
-      <c r="H41" s="25"/>
+        <v>31</v>
+      </c>
+      <c r="G41" s="25"/>
+      <c r="H41" s="26"/>
     </row>
     <row r="42">
-      <c r="A42" s="45"/>
+      <c r="A42" s="46"/>
       <c r="B42" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
+        <v>97</v>
+      </c>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
       <c r="F42" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="G42" s="24"/>
-      <c r="H42" s="25"/>
+        <v>31</v>
+      </c>
+      <c r="G42" s="25"/>
+      <c r="H42" s="26"/>
     </row>
     <row r="43">
-      <c r="A43" s="45"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="25"/>
+      <c r="A43" s="46"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="26"/>
     </row>
     <row r="44">
-      <c r="A44" s="45"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="25"/>
+      <c r="A44" s="46"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="26"/>
     </row>
     <row r="45">
-      <c r="A45" s="45"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="25"/>
+      <c r="A45" s="46"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="26"/>
     </row>
     <row r="46">
-      <c r="A46" s="45"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="25"/>
+      <c r="A46" s="46"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="26"/>
     </row>
     <row r="47">
-      <c r="A47" s="45"/>
-      <c r="B47" s="49"/>
-      <c r="C47" s="49"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="50"/>
+      <c r="A47" s="46"/>
+      <c r="B47" s="50"/>
+      <c r="C47" s="50"/>
+      <c r="D47" s="50"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="50"/>
+      <c r="G47" s="51"/>
       <c r="H47" s="7"/>
     </row>
   </sheetData>
